--- a/作成中事業計画書/新20261001【更新版】★20260930スケジュール（トンボ飲料様）.xlsx
+++ b/作成中事業計画書/新20261001【更新版】★20260930スケジュール（トンボ飲料様）.xlsx
@@ -300,7 +300,8 @@
 賃上げ</t>
   </si>
   <si>
-    <t>統括責任者</t>
+    <t xml:space="preserve">事業責任者（社長）
+統括責任者</t>
   </si>
   <si>
     <t>取組項目</t>
@@ -374,7 +375,7 @@
     <t>５．賃上げ</t>
   </si>
   <si>
-    <t>統括責任者は、採択後から交付申請までに、賃上げ計画（足下の賃上げを含む）を全ての従業員（または従業員代表者）と役員へ表明する。
+    <t>事業責任者（社長）は、採択後から交付申請までに、賃上げ計画（足下の賃上げを含む）を全ての従業員（または従業員代表者）と役員へ表明する（統括責任者が準備する）。
 1人当たり給与支給総額は、足下（2028年3月期まで）は年3%、基準年度以降は年平均3.5%以上引き上げる。
 事業場内最低賃金は、要件の判定時点である毎年3月末に富山県最低賃金＋30円以上となるよう、毎年3月までに見直して引き上げる（初回は2027年3月までに1,150円以上。県最低賃金は2026年10月から1,119円）。</t>
   </si>
@@ -3303,7 +3304,7 @@
       <c r="AQ25" s="15"/>
       <c r="AR25" s="17"/>
     </row>
-    <row r="26" spans="2:44" ht="22" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:44" ht="44" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="63" t="s">
         <v>49</v>
       </c>
